--- a/docs/data/raw/2026-05-31_ST.xlsx
+++ b/docs/data/raw/2026-05-31_ST.xlsx
@@ -536,36 +536,36 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>L244</t>
+          <t>K315</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SPICE BAG</t>
+          <t>LOOKING BRIGHT</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>J Orman</t>
+          <t>P N Wong (-7)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>D J Hall</t>
+          <t>F C Lor</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11/8/5/2/12/3</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -594,36 +594,36 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>L245</t>
+          <t>L169</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ALMIGHTY WARRIOR</t>
+          <t>GIANT SPIRIT</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>E Brown</t>
+          <t>H T Mo (-2)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>K W Lui</t>
+          <t>Y S Tsui</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11/7/12/13/14</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -652,36 +652,36 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>L051</t>
+          <t>L105</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CHANCHENG SPARKLE</t>
+          <t>ONESHOT</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J4" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C L Chau (-2)</t>
+          <t>K Teetan</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>K W Lui</t>
+          <t>W K Mo</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1/14/5</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -710,36 +710,36 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>L307</t>
+          <t>K291</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>COOGEE BAY</t>
+          <t>THE ALL OUT</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>J Orman</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>P C Ng</t>
+          <t>J Richards</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/10/11/10/5/10</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -768,36 +768,36 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>L306</t>
+          <t>J323</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>GOLDEN GUNNERS</t>
+          <t>GRAND NOVA</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>E C W Wong (-3)</t>
+          <t>H Bowman</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>C Fownes</t>
+          <t>J Size</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2/12/2/4/3/9</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -826,36 +826,36 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>L308</t>
+          <t>L291</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SHARP PLANET</t>
+          <t>DOUBLE ALPHA</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>J Moreira</t>
+          <t>M F Poon</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>C Fownes</t>
+          <t>C S Shum</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -884,36 +884,36 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>L355</t>
+          <t>L389</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SHOW ME YOUR LOVE</t>
+          <t>GALLANT BOUNTY</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>H Bowman</t>
+          <t>B Avdulla</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>D J Whyte</t>
+          <t>D A Hayes</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -942,36 +942,36 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>L236</t>
+          <t>L137</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SILVERY KNIGHT</t>
+          <t>KA YING LIGHTNING</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L Hewitson</t>
+          <t>A Atzeni</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>D J Whyte</t>
+          <t>D J Hall</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>8/4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1000,36 +1000,36 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>L317</t>
+          <t>L254</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>EVER WEALTH</t>
+          <t>KING'S ARROW</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>H Y Yuen (-10)</t>
+          <t>L Hewitson</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>P F Yiu</t>
+          <t>B Crawford</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -1058,36 +1058,36 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>L345</t>
+          <t>L179</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>GAUDIUM MAGNUM</t>
+          <t>STORM MIRROR</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>A Atzeni</t>
+          <t>Z Purton</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>M Newnham</t>
+          <t>P C Ng</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -1116,32 +1116,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>L393</t>
+          <t>L146</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>QUANTUM WUKONG</t>
+          <t>TURF QUEST</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Y L Chung (-2)</t>
+          <t>M L Yeung</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>A S Cruz</t>
+          <t>W Y So</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1174,36 +1174,36 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>L276</t>
+          <t>L201</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>RISING WORLD</t>
+          <t>CASA PRIMO</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Z Purton</t>
+          <t>H Bentley</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>B Crawford</t>
+          <t>C W Chang</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5/5/5</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1232,36 +1232,36 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>L290</t>
+          <t>K529</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SECRET INGREDIENT</t>
+          <t>JUMBO BLESSING</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J14" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>H Bentley</t>
+          <t>J Moreira</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>D A Hayes</t>
+          <t>C Fownes</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>10/2</t>
+          <t>7/5/12/4</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1290,39 +1290,43 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>L295</t>
+          <t>K377</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TALENTS CHAMPION</t>
+          <t>QUICK MONEY</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>C Y Ho</t>
+          <t>M Chadwick</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>D A Hayes</t>
+          <t>C H Yip</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>7/3</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>11/13/13/6/10/7</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="n">
         <v>20</v>
       </c>
@@ -7467,7 +7471,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J121" t="n">
         <v>130</v>
@@ -7525,7 +7529,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J122" t="n">
         <v>130</v>
@@ -7583,7 +7587,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J123" t="n">
         <v>129</v>
@@ -7641,7 +7645,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J124" t="n">
         <v>126</v>
@@ -7927,36 +7931,36 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>TRINITY TREASURE</t>
+          <t>TRINITY TREASURE(Scratched)</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Z Purton</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>D Eustace</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M129" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -8051,7 +8055,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J131" t="n">
         <v>115</v>
@@ -9748,7 +9752,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>130</v>
@@ -9779,7 +9783,7 @@
         <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="5">
@@ -9799,7 +9803,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>130</v>
@@ -9830,7 +9834,7 @@
         <v>14</v>
       </c>
       <c r="M5" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="6">
@@ -9850,7 +9854,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>129</v>
@@ -9881,7 +9885,7 @@
         <v>14</v>
       </c>
       <c r="M6" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -9901,7 +9905,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>126</v>
@@ -9932,7 +9936,7 @@
         <v>14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="8">
@@ -10152,36 +10156,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TRINITY TREASURE</t>
+          <t>TRINITY TREASURE(Scratched)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Z Purton</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>D Eustace</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -10191,7 +10195,7 @@
         <v>14</v>
       </c>
       <c r="M12" t="n">
-        <v>0.96</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="13">
@@ -10262,7 +10266,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
         <v>115</v>
@@ -10293,7 +10297,7 @@
         <v>14</v>
       </c>
       <c r="M14" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="15">
@@ -19314,36 +19318,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L244</t>
+          <t>K315</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SPICE BAG</t>
+          <t>LOOKING BRIGHT</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>J Orman</t>
+          <t>P N Wong (-7)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>D J Hall</t>
+          <t>F C Lor</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11/8/5/2/12/3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -19354,7 +19358,7 @@
         <v>14</v>
       </c>
       <c r="M2" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="3">
@@ -19365,36 +19369,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>L245</t>
+          <t>L169</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ALMIGHTY WARRIOR</t>
+          <t>GIANT SPIRIT</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>E Brown</t>
+          <t>H T Mo (-2)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>K W Lui</t>
+          <t>Y S Tsui</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11/7/12/13/14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -19405,7 +19409,7 @@
         <v>14</v>
       </c>
       <c r="M3" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -19416,36 +19420,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L051</t>
+          <t>L105</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CHANCHENG SPARKLE</t>
+          <t>ONESHOT</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C L Chau (-2)</t>
+          <t>K Teetan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>K W Lui</t>
+          <t>W K Mo</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1/14/5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -19456,7 +19460,7 @@
         <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="5">
@@ -19467,36 +19471,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L307</t>
+          <t>K291</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>COOGEE BAY</t>
+          <t>THE ALL OUT</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>J Orman</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>P C Ng</t>
+          <t>J Richards</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/10/11/10/5/10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -19507,7 +19511,7 @@
         <v>14</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -19518,36 +19522,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L306</t>
+          <t>J323</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GOLDEN GUNNERS</t>
+          <t>GRAND NOVA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>E C W Wong (-3)</t>
+          <t>H Bowman</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C Fownes</t>
+          <t>J Size</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2/12/2/4/3/9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -19558,7 +19562,7 @@
         <v>14</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="7">
@@ -19569,36 +19573,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L308</t>
+          <t>L291</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SHARP PLANET</t>
+          <t>DOUBLE ALPHA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>J Moreira</t>
+          <t>M F Poon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C Fownes</t>
+          <t>C S Shum</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -19609,7 +19613,7 @@
         <v>14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="8">
@@ -19620,36 +19624,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L355</t>
+          <t>L389</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SHOW ME YOUR LOVE</t>
+          <t>GALLANT BOUNTY</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>H Bowman</t>
+          <t>B Avdulla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>D J Whyte</t>
+          <t>D A Hayes</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -19660,7 +19664,7 @@
         <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="9">
@@ -19671,36 +19675,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L236</t>
+          <t>L137</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SILVERY KNIGHT</t>
+          <t>KA YING LIGHTNING</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>L Hewitson</t>
+          <t>A Atzeni</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>D J Whyte</t>
+          <t>D J Hall</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8/4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -19711,7 +19715,7 @@
         <v>14</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="10">
@@ -19722,36 +19726,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L317</t>
+          <t>L254</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EVER WEALTH</t>
+          <t>KING'S ARROW</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>H Y Yuen (-10)</t>
+          <t>L Hewitson</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>P F Yiu</t>
+          <t>B Crawford</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -19762,7 +19766,7 @@
         <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="11">
@@ -19773,36 +19777,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L345</t>
+          <t>L179</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GAUDIUM MAGNUM</t>
+          <t>STORM MIRROR</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>A Atzeni</t>
+          <t>Z Purton</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>M Newnham</t>
+          <t>P C Ng</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -19813,7 +19817,7 @@
         <v>14</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="12">
@@ -19824,32 +19828,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L393</t>
+          <t>L146</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>QUANTUM WUKONG</t>
+          <t>TURF QUEST</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Y L Chung (-2)</t>
+          <t>M L Yeung</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A S Cruz</t>
+          <t>W Y So</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -19864,7 +19868,7 @@
         <v>14</v>
       </c>
       <c r="M12" t="n">
-        <v>0.82</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="13">
@@ -19875,36 +19879,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L276</t>
+          <t>L201</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RISING WORLD</t>
+          <t>CASA PRIMO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Z Purton</t>
+          <t>H Bentley</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B Crawford</t>
+          <t>C W Chang</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5/5/5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -19915,7 +19919,7 @@
         <v>14</v>
       </c>
       <c r="M13" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="14">
@@ -19926,36 +19930,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L290</t>
+          <t>K529</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SECRET INGREDIENT</t>
+          <t>JUMBO BLESSING</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>H Bentley</t>
+          <t>J Moreira</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>D A Hayes</t>
+          <t>C Fownes</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10/2</t>
+          <t>7/5/12/4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -19966,7 +19970,7 @@
         <v>14</v>
       </c>
       <c r="M14" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15">
@@ -19977,39 +19981,43 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L295</t>
+          <t>K377</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TALENTS CHAMPION</t>
+          <t>QUICK MONEY</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C Y Ho</t>
+          <t>M Chadwick</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>D A Hayes</t>
+          <t>C H Yip</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7/3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>11/13/13/6/10/7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="n">
         <v>20</v>
       </c>
@@ -20017,7 +20025,7 @@
         <v>14</v>
       </c>
       <c r="M15" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>
